--- a/template/t9_ocr_report.xlsx
+++ b/template/t9_ocr_report.xlsx
@@ -85,7 +85,7 @@
     <t>micro_0005_S4.jpg</t>
   </si>
   <si>
-    <t>micro_0035_S3.jpg</t>
+    <t>micro_0013_S3.jpg</t>
   </si>
   <si>
     <t>micro_0026_S.jpg</t>
@@ -628,7 +628,7 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8685481548309326</v>
       </c>
       <c r="D2" t="s">
         <v>75</v>
@@ -637,13 +637,13 @@
         <v>2</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>24.25180598555212</v>
+        <v>0</v>
       </c>
       <c r="I2" t="s">
         <v>76</v>
@@ -669,7 +669,7 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>0.9508761763572693</v>
+        <v>0.8731943964958191</v>
       </c>
       <c r="D3" t="s">
         <v>75</v>
@@ -710,7 +710,7 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.996694028377533</v>
       </c>
       <c r="D4" t="s">
         <v>75</v>
@@ -751,7 +751,7 @@
         <v>47</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.9901691675186157</v>
       </c>
       <c r="D5" t="s">
         <v>75</v>
@@ -760,13 +760,13 @@
         <v>2</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>26.42543859649123</v>
+        <v>0</v>
       </c>
       <c r="I5" t="s">
         <v>76</v>
@@ -792,7 +792,7 @@
         <v>48</v>
       </c>
       <c r="C6">
-        <v>0.9958783388137817</v>
+        <v>0.9878877401351929</v>
       </c>
       <c r="D6" t="s">
         <v>75</v>
@@ -801,13 +801,13 @@
         <v>2</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>23.16136114160264</v>
+        <v>0</v>
       </c>
       <c r="I6" t="s">
         <v>76</v>
@@ -833,7 +833,7 @@
         <v>49</v>
       </c>
       <c r="C7">
-        <v>0.7695338129997253</v>
+        <v>0.9867039918899536</v>
       </c>
       <c r="D7" t="s">
         <v>75</v>
@@ -883,13 +883,13 @@
         <v>2</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>25.5026455026455</v>
+        <v>0</v>
       </c>
       <c r="I8" t="s">
         <v>76</v>
@@ -924,13 +924,13 @@
         <v>2</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>25.77962577962578</v>
+        <v>0</v>
       </c>
       <c r="I9" t="s">
         <v>76</v>
@@ -1006,13 +1006,13 @@
         <v>2</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>18.85576148267526</v>
+        <v>0</v>
       </c>
       <c r="I11" t="s">
         <v>76</v>
@@ -1038,7 +1038,7 @@
         <v>54</v>
       </c>
       <c r="C12">
-        <v>0.8262888193130493</v>
+        <v>0.9702445268630981</v>
       </c>
       <c r="D12" t="s">
         <v>75</v>
@@ -1047,13 +1047,13 @@
         <v>2</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>24.73429951690821</v>
+        <v>0</v>
       </c>
       <c r="I12" t="s">
         <v>76</v>
@@ -1120,7 +1120,7 @@
         <v>56</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0.8569714426994324</v>
       </c>
       <c r="D14" t="s">
         <v>75</v>
@@ -1264,13 +1264,13 @@
         <v>76</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -1551,13 +1551,13 @@
         <v>76</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>1</v>
@@ -1633,13 +1633,13 @@
         <v>76</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:13">

--- a/template/t9_ocr_report.xlsx
+++ b/template/t9_ocr_report.xlsx
@@ -85,7 +85,7 @@
     <t>micro_0005_S4.jpg</t>
   </si>
   <si>
-    <t>micro_0013_S3.jpg</t>
+    <t>micro_0035_S3.jpg</t>
   </si>
   <si>
     <t>micro_0026_S.jpg</t>
@@ -628,7 +628,7 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>0.8685481548309326</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>75</v>
@@ -637,13 +637,13 @@
         <v>2</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>24.25180598555212</v>
       </c>
       <c r="I2" t="s">
         <v>76</v>
@@ -669,7 +669,7 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>0.8731943964958191</v>
+        <v>0.9508761763572693</v>
       </c>
       <c r="D3" t="s">
         <v>75</v>
@@ -710,7 +710,7 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>0.996694028377533</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>75</v>
@@ -751,7 +751,7 @@
         <v>47</v>
       </c>
       <c r="C5">
-        <v>0.9901691675186157</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>75</v>
@@ -760,13 +760,13 @@
         <v>2</v>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>26.42543859649123</v>
       </c>
       <c r="I5" t="s">
         <v>76</v>
@@ -792,7 +792,7 @@
         <v>48</v>
       </c>
       <c r="C6">
-        <v>0.9878877401351929</v>
+        <v>0.9958783388137817</v>
       </c>
       <c r="D6" t="s">
         <v>75</v>
@@ -801,13 +801,13 @@
         <v>2</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>23.16136114160264</v>
       </c>
       <c r="I6" t="s">
         <v>76</v>
@@ -833,7 +833,7 @@
         <v>49</v>
       </c>
       <c r="C7">
-        <v>0.9867039918899536</v>
+        <v>0.7695338129997253</v>
       </c>
       <c r="D7" t="s">
         <v>75</v>
@@ -883,13 +883,13 @@
         <v>2</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>25.5026455026455</v>
       </c>
       <c r="I8" t="s">
         <v>76</v>
@@ -924,13 +924,13 @@
         <v>2</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>25.77962577962578</v>
       </c>
       <c r="I9" t="s">
         <v>76</v>
@@ -1006,13 +1006,13 @@
         <v>2</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>18.85576148267526</v>
       </c>
       <c r="I11" t="s">
         <v>76</v>
@@ -1038,7 +1038,7 @@
         <v>54</v>
       </c>
       <c r="C12">
-        <v>0.9702445268630981</v>
+        <v>0.8262888193130493</v>
       </c>
       <c r="D12" t="s">
         <v>75</v>
@@ -1047,13 +1047,13 @@
         <v>2</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>24.73429951690821</v>
       </c>
       <c r="I12" t="s">
         <v>76</v>
@@ -1120,7 +1120,7 @@
         <v>56</v>
       </c>
       <c r="C14">
-        <v>0.8569714426994324</v>
+        <v>1</v>
       </c>
       <c r="D14" t="s">
         <v>75</v>
@@ -1264,13 +1264,13 @@
         <v>76</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -1551,13 +1551,13 @@
         <v>76</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24">
         <v>1</v>
@@ -1633,13 +1633,13 @@
         <v>76</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:13">

--- a/template/t9_ocr_report.xlsx
+++ b/template/t9_ocr_report.xlsx
@@ -85,7 +85,7 @@
     <t>micro_0005_S4.jpg</t>
   </si>
   <si>
-    <t>micro_0035_S3.jpg</t>
+    <t>micro_0013_S3.jpg</t>
   </si>
   <si>
     <t>micro_0026_S.jpg</t>
@@ -628,7 +628,7 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8170149326324463</v>
       </c>
       <c r="D2" t="s">
         <v>75</v>
@@ -637,13 +637,13 @@
         <v>2</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>24.25180598555212</v>
+        <v>0</v>
       </c>
       <c r="I2" t="s">
         <v>76</v>
@@ -669,7 +669,7 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>0.9508761763572693</v>
+        <v>0.7785676121711731</v>
       </c>
       <c r="D3" t="s">
         <v>75</v>
@@ -710,7 +710,7 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.9974875450134277</v>
       </c>
       <c r="D4" t="s">
         <v>75</v>
@@ -751,7 +751,7 @@
         <v>47</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.9954218864440918</v>
       </c>
       <c r="D5" t="s">
         <v>75</v>
@@ -760,13 +760,13 @@
         <v>2</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>26.42543859649123</v>
+        <v>0</v>
       </c>
       <c r="I5" t="s">
         <v>76</v>
@@ -792,7 +792,7 @@
         <v>48</v>
       </c>
       <c r="C6">
-        <v>0.9958783388137817</v>
+        <v>0.9854831695556641</v>
       </c>
       <c r="D6" t="s">
         <v>75</v>
@@ -801,13 +801,13 @@
         <v>2</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>23.16136114160264</v>
+        <v>0</v>
       </c>
       <c r="I6" t="s">
         <v>76</v>
@@ -833,7 +833,7 @@
         <v>49</v>
       </c>
       <c r="C7">
-        <v>0.7695338129997253</v>
+        <v>0.9685484766960144</v>
       </c>
       <c r="D7" t="s">
         <v>75</v>
@@ -883,13 +883,13 @@
         <v>2</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>25.5026455026455</v>
+        <v>0</v>
       </c>
       <c r="I8" t="s">
         <v>76</v>
@@ -924,13 +924,13 @@
         <v>2</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>25.77962577962578</v>
+        <v>0</v>
       </c>
       <c r="I9" t="s">
         <v>76</v>
@@ -1006,13 +1006,13 @@
         <v>2</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>18.85576148267526</v>
+        <v>0</v>
       </c>
       <c r="I11" t="s">
         <v>76</v>
@@ -1038,7 +1038,7 @@
         <v>54</v>
       </c>
       <c r="C12">
-        <v>0.8262888193130493</v>
+        <v>0.9702445268630981</v>
       </c>
       <c r="D12" t="s">
         <v>75</v>
@@ -1047,13 +1047,13 @@
         <v>2</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>24.73429951690821</v>
+        <v>0</v>
       </c>
       <c r="I12" t="s">
         <v>76</v>
@@ -1120,7 +1120,7 @@
         <v>56</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0.8503179550170898</v>
       </c>
       <c r="D14" t="s">
         <v>75</v>
@@ -1264,13 +1264,13 @@
         <v>76</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -1551,13 +1551,13 @@
         <v>76</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>1</v>
@@ -1633,13 +1633,13 @@
         <v>76</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:13">

--- a/template/t9_ocr_report.xlsx
+++ b/template/t9_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="78">
   <si>
     <t>filename</t>
   </si>
@@ -55,6 +55,9 @@
     <t>blue_centers</t>
   </si>
   <si>
+    <t>white_centers</t>
+  </si>
+  <si>
     <t>micro_0049_XII.jpg</t>
   </si>
   <si>
@@ -85,7 +88,7 @@
     <t>micro_0005_S4.jpg</t>
   </si>
   <si>
-    <t>micro_0013_S3.jpg</t>
+    <t>micro_0035_S3.jpg</t>
   </si>
   <si>
     <t>micro_0026_S.jpg</t>
@@ -576,10 +579,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -619,19 +622,22 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>0.8170149326324463</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -646,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -660,19 +666,22 @@
       <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>0.7785676121711731</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -687,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -701,19 +710,22 @@
       <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>0.9974875450134277</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -728,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -742,19 +754,22 @@
       <c r="M4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5">
         <v>0.9954218864440918</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -769,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -783,19 +798,22 @@
       <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6">
         <v>0.9854831695556641</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -810,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -824,19 +842,22 @@
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>0.9685484766960144</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -851,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -865,19 +886,22 @@
       <c r="M7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8">
-        <v>0.9135814309120178</v>
+        <v>0.8611977100372314</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -892,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -906,19 +930,22 @@
       <c r="M8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9">
-        <v>0.8664977550506592</v>
+        <v>0.9470760822296143</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -933,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -947,19 +974,22 @@
       <c r="M9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10">
-        <v>0.9706487059593201</v>
+        <v>0.9956051707267761</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -974,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -988,19 +1018,22 @@
       <c r="M10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11">
-        <v>0.9968549013137817</v>
+        <v>0.9962334036827087</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1015,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1029,19 +1062,22 @@
       <c r="M11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12">
-        <v>0.9702445268630981</v>
+        <v>0.9953106641769409</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1056,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1070,19 +1106,22 @@
       <c r="M12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13">
-        <v>0.9665384888648987</v>
+        <v>0.9655420184135437</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1097,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1111,757 +1150,814 @@
       <c r="M13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14">
-        <v>0.8503179550170898</v>
+        <v>0.9048388004302979</v>
       </c>
       <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15">
+        <v>0.8947662115097046</v>
+      </c>
+      <c r="D15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16">
+        <v>0.994773268699646</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17">
+        <v>0.994149923324585</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18">
+        <v>0.9943592548370361</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19">
+        <v>0.998421847820282</v>
+      </c>
+      <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20">
+        <v>0.9920345544815063</v>
+      </c>
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21">
+        <v>0.9973452091217041</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>77</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22">
+        <v>0.9946379661560059</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>77</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23">
+        <v>0.9765729904174805</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" t="s">
+        <v>77</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24">
+        <v>0.9976012706756592</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>77</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25">
+        <v>0.9946244359016418</v>
+      </c>
+      <c r="D25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26">
+        <v>0.9979330897331238</v>
+      </c>
+      <c r="D26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" t="s">
+        <v>77</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27">
+        <v>0.9976310729980469</v>
+      </c>
+      <c r="D27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>77</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28">
+        <v>0.9988123774528503</v>
+      </c>
+      <c r="D28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" t="s">
+        <v>77</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29">
+        <v>0.9974618554115295</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" t="s">
+        <v>77</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30">
+        <v>0.9959304928779602</v>
+      </c>
+      <c r="D30" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
+        <v>77</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31">
+        <v>0.9654316902160645</v>
+      </c>
+      <c r="D31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>77</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" t="s">
         <v>75</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15">
-        <v>0.93854820728302</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17">
-        <v>2</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18" t="s">
-        <v>76</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" t="s">
-        <v>76</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20" t="s">
-        <v>76</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21" t="s">
-        <v>76</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22" t="s">
-        <v>76</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23" t="s">
-        <v>76</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25" t="s">
-        <v>76</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26" t="s">
-        <v>76</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27" t="s">
-        <v>76</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28" t="s">
-        <v>76</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29" t="s">
-        <v>76</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" t="s">
-        <v>76</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31" t="s">
-        <v>76</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" t="s">
-        <v>74</v>
-      </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1876,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1889,6 +1985,9 @@
       </c>
       <c r="M32">
         <v>1</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/template/t9_ocr_report.xlsx
+++ b/template/t9_ocr_report.xlsx
@@ -634,7 +634,7 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>0.8170149326324463</v>
+        <v>0.8281568288803101</v>
       </c>
       <c r="D2" t="s">
         <v>76</v>
@@ -678,7 +678,7 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>0.7785676121711731</v>
+        <v>0.788079559803009</v>
       </c>
       <c r="D3" t="s">
         <v>76</v>
@@ -722,7 +722,7 @@
         <v>47</v>
       </c>
       <c r="C4">
-        <v>0.9974875450134277</v>
+        <v>0.9956420063972473</v>
       </c>
       <c r="D4" t="s">
         <v>76</v>
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -766,7 +766,7 @@
         <v>48</v>
       </c>
       <c r="C5">
-        <v>0.9954218864440918</v>
+        <v>0.9937313795089722</v>
       </c>
       <c r="D5" t="s">
         <v>76</v>
@@ -810,7 +810,7 @@
         <v>49</v>
       </c>
       <c r="C6">
-        <v>0.9854831695556641</v>
+        <v>0.9877424240112305</v>
       </c>
       <c r="D6" t="s">
         <v>76</v>
@@ -898,7 +898,7 @@
         <v>51</v>
       </c>
       <c r="C8">
-        <v>0.8611977100372314</v>
+        <v>0.8643468022346497</v>
       </c>
       <c r="D8" t="s">
         <v>76</v>
@@ -942,7 +942,7 @@
         <v>52</v>
       </c>
       <c r="C9">
-        <v>0.9470760822296143</v>
+        <v>0.9624366760253906</v>
       </c>
       <c r="D9" t="s">
         <v>76</v>
@@ -986,7 +986,7 @@
         <v>53</v>
       </c>
       <c r="C10">
-        <v>0.9956051707267761</v>
+        <v>0.9957809448242188</v>
       </c>
       <c r="D10" t="s">
         <v>76</v>
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1030,7 +1030,7 @@
         <v>54</v>
       </c>
       <c r="C11">
-        <v>0.9962334036827087</v>
+        <v>0.997520923614502</v>
       </c>
       <c r="D11" t="s">
         <v>76</v>
@@ -1063,7 +1063,7 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1074,7 +1074,7 @@
         <v>55</v>
       </c>
       <c r="C12">
-        <v>0.9953106641769409</v>
+        <v>0.9944437146186829</v>
       </c>
       <c r="D12" t="s">
         <v>76</v>
@@ -1118,7 +1118,7 @@
         <v>56</v>
       </c>
       <c r="C13">
-        <v>0.9655420184135437</v>
+        <v>0.9691565036773682</v>
       </c>
       <c r="D13" t="s">
         <v>76</v>
@@ -1148,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>0.9048388004302979</v>
+        <v>0.9130418300628662</v>
       </c>
       <c r="D14" t="s">
         <v>76</v>
@@ -1206,7 +1206,7 @@
         <v>58</v>
       </c>
       <c r="C15">
-        <v>0.8947662115097046</v>
+        <v>0.9508355259895325</v>
       </c>
       <c r="D15" t="s">
         <v>76</v>
@@ -1250,7 +1250,7 @@
         <v>59</v>
       </c>
       <c r="C16">
-        <v>0.994773268699646</v>
+        <v>0.9949803352355957</v>
       </c>
       <c r="D16" t="s">
         <v>76</v>
@@ -1274,16 +1274,16 @@
         <v>1</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1294,7 +1294,7 @@
         <v>60</v>
       </c>
       <c r="C17">
-        <v>0.994149923324585</v>
+        <v>0.9940155744552612</v>
       </c>
       <c r="D17" t="s">
         <v>76</v>
@@ -1338,7 +1338,7 @@
         <v>61</v>
       </c>
       <c r="C18">
-        <v>0.9943592548370361</v>
+        <v>0.9946953058242798</v>
       </c>
       <c r="D18" t="s">
         <v>76</v>
@@ -1382,7 +1382,7 @@
         <v>62</v>
       </c>
       <c r="C19">
-        <v>0.998421847820282</v>
+        <v>0.9986534118652344</v>
       </c>
       <c r="D19" t="s">
         <v>76</v>
@@ -1426,7 +1426,7 @@
         <v>63</v>
       </c>
       <c r="C20">
-        <v>0.9920345544815063</v>
+        <v>0.9924682974815369</v>
       </c>
       <c r="D20" t="s">
         <v>76</v>
@@ -1470,7 +1470,7 @@
         <v>64</v>
       </c>
       <c r="C21">
-        <v>0.9973452091217041</v>
+        <v>0.9967378377914429</v>
       </c>
       <c r="D21" t="s">
         <v>76</v>
@@ -1514,7 +1514,7 @@
         <v>65</v>
       </c>
       <c r="C22">
-        <v>0.9946379661560059</v>
+        <v>0.9970628023147583</v>
       </c>
       <c r="D22" t="s">
         <v>76</v>
@@ -1535,13 +1535,13 @@
         <v>77</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         <v>66</v>
       </c>
       <c r="C23">
-        <v>0.9765729904174805</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
         <v>76</v>
@@ -1602,7 +1602,7 @@
         <v>67</v>
       </c>
       <c r="C24">
-        <v>0.9976012706756592</v>
+        <v>0.997830331325531</v>
       </c>
       <c r="D24" t="s">
         <v>76</v>
@@ -1646,7 +1646,7 @@
         <v>68</v>
       </c>
       <c r="C25">
-        <v>0.9946244359016418</v>
+        <v>0.9920629858970642</v>
       </c>
       <c r="D25" t="s">
         <v>76</v>
@@ -1690,7 +1690,7 @@
         <v>69</v>
       </c>
       <c r="C26">
-        <v>0.9979330897331238</v>
+        <v>0.9977728724479675</v>
       </c>
       <c r="D26" t="s">
         <v>76</v>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -1734,7 +1734,7 @@
         <v>70</v>
       </c>
       <c r="C27">
-        <v>0.9976310729980469</v>
+        <v>0.9963591694831848</v>
       </c>
       <c r="D27" t="s">
         <v>76</v>
@@ -1778,7 +1778,7 @@
         <v>71</v>
       </c>
       <c r="C28">
-        <v>0.9988123774528503</v>
+        <v>0.9988676905632019</v>
       </c>
       <c r="D28" t="s">
         <v>76</v>
@@ -1822,7 +1822,7 @@
         <v>72</v>
       </c>
       <c r="C29">
-        <v>0.9974618554115295</v>
+        <v>0.9974004626274109</v>
       </c>
       <c r="D29" t="s">
         <v>76</v>
@@ -1866,7 +1866,7 @@
         <v>73</v>
       </c>
       <c r="C30">
-        <v>0.9959304928779602</v>
+        <v>0.9958569407463074</v>
       </c>
       <c r="D30" t="s">
         <v>76</v>
@@ -1910,7 +1910,7 @@
         <v>74</v>
       </c>
       <c r="C31">
-        <v>0.9654316902160645</v>
+        <v>0.9776134490966797</v>
       </c>
       <c r="D31" t="s">
         <v>76</v>

--- a/template/t9_ocr_report.xlsx
+++ b/template/t9_ocr_report.xlsx
@@ -1338,7 +1338,7 @@
         <v>61</v>
       </c>
       <c r="C18">
-        <v>0.9943592548370361</v>
+        <v>0.9946953058242798</v>
       </c>
       <c r="D18" t="s">
         <v>76</v>
@@ -1382,7 +1382,7 @@
         <v>62</v>
       </c>
       <c r="C19">
-        <v>0.998421847820282</v>
+        <v>0.9986534118652344</v>
       </c>
       <c r="D19" t="s">
         <v>76</v>
@@ -1426,7 +1426,7 @@
         <v>63</v>
       </c>
       <c r="C20">
-        <v>0.9920345544815063</v>
+        <v>0.9924682974815369</v>
       </c>
       <c r="D20" t="s">
         <v>76</v>
@@ -1470,7 +1470,7 @@
         <v>64</v>
       </c>
       <c r="C21">
-        <v>0.9973452091217041</v>
+        <v>0.9967378377914429</v>
       </c>
       <c r="D21" t="s">
         <v>76</v>
@@ -1514,7 +1514,7 @@
         <v>65</v>
       </c>
       <c r="C22">
-        <v>0.9946379661560059</v>
+        <v>0.9970628023147583</v>
       </c>
       <c r="D22" t="s">
         <v>76</v>
@@ -1535,13 +1535,13 @@
         <v>77</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         <v>66</v>
       </c>
       <c r="C23">
-        <v>0.9765729904174805</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
         <v>76</v>
@@ -1602,7 +1602,7 @@
         <v>67</v>
       </c>
       <c r="C24">
-        <v>0.9976012706756592</v>
+        <v>0.997830331325531</v>
       </c>
       <c r="D24" t="s">
         <v>76</v>
@@ -1646,7 +1646,7 @@
         <v>68</v>
       </c>
       <c r="C25">
-        <v>0.9946244359016418</v>
+        <v>0.9920629858970642</v>
       </c>
       <c r="D25" t="s">
         <v>76</v>
@@ -1690,7 +1690,7 @@
         <v>69</v>
       </c>
       <c r="C26">
-        <v>0.9979330897331238</v>
+        <v>0.9977728724479675</v>
       </c>
       <c r="D26" t="s">
         <v>76</v>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -1734,7 +1734,7 @@
         <v>70</v>
       </c>
       <c r="C27">
-        <v>0.9976310729980469</v>
+        <v>0.9963591694831848</v>
       </c>
       <c r="D27" t="s">
         <v>76</v>
@@ -1778,7 +1778,7 @@
         <v>71</v>
       </c>
       <c r="C28">
-        <v>0.9988123774528503</v>
+        <v>0.9988676905632019</v>
       </c>
       <c r="D28" t="s">
         <v>76</v>
@@ -1822,7 +1822,7 @@
         <v>72</v>
       </c>
       <c r="C29">
-        <v>0.9974618554115295</v>
+        <v>0.9974004626274109</v>
       </c>
       <c r="D29" t="s">
         <v>76</v>
@@ -1866,7 +1866,7 @@
         <v>73</v>
       </c>
       <c r="C30">
-        <v>0.9959304928779602</v>
+        <v>0.9958569407463074</v>
       </c>
       <c r="D30" t="s">
         <v>76</v>
@@ -1910,7 +1910,7 @@
         <v>74</v>
       </c>
       <c r="C31">
-        <v>0.9654316902160645</v>
+        <v>0.9776134490966797</v>
       </c>
       <c r="D31" t="s">
         <v>76</v>

--- a/template/t9_ocr_report.xlsx
+++ b/template/t9_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="80">
   <si>
     <t>filename</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>white_centers</t>
+  </si>
+  <si>
+    <t>is_tri</t>
+  </si>
+  <si>
+    <t>is_double</t>
   </si>
   <si>
     <t>micro_0049_XII.jpg</t>
@@ -579,10 +585,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -625,19 +631,25 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C2">
         <v>0.8170149326324463</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -652,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -669,19 +681,25 @@
       <c r="N2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C3">
-        <v>0.7785676121711731</v>
+        <v>0.8569067716598511</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -696,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -713,19 +731,25 @@
       <c r="N3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
-        <v>0.9974875450134277</v>
+        <v>0.9116420149803162</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -740,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -757,19 +781,25 @@
       <c r="N4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>0.9954218864440918</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -784,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -801,19 +831,25 @@
       <c r="N5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>0.9854831695556641</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -828,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -845,19 +881,25 @@
       <c r="N6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -872,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -889,19 +931,25 @@
       <c r="N7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>0.8611977100372314</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -916,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -933,19 +981,25 @@
       <c r="N8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9">
         <v>0.9470760822296143</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -960,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -977,19 +1031,25 @@
       <c r="N9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C10">
         <v>0.9956051707267761</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1004,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1021,19 +1081,25 @@
       <c r="N10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C11">
         <v>0.9962334036827087</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1048,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1065,19 +1131,25 @@
       <c r="N11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12">
         <v>0.9953106641769409</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1092,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1109,19 +1181,25 @@
       <c r="N12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C13">
         <v>0.9655420184135437</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1136,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1153,19 +1231,25 @@
       <c r="N13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>0.9048388004302979</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1180,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1197,19 +1281,25 @@
       <c r="N14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C15">
         <v>0.8947662115097046</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1224,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1241,19 +1331,25 @@
       <c r="N15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C16">
         <v>0.994773268699646</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1268,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1285,19 +1381,25 @@
       <c r="N16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C17">
         <v>0.994149923324585</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1312,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1329,19 +1431,25 @@
       <c r="N17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C18">
         <v>0.9946953058242798</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1356,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1373,19 +1481,25 @@
       <c r="N18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C19">
         <v>0.9986534118652344</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1400,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1417,19 +1531,25 @@
       <c r="N19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20">
         <v>0.9924682974815369</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1444,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1461,19 +1581,25 @@
       <c r="N20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C21">
         <v>0.9967378377914429</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1488,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1505,19 +1631,25 @@
       <c r="N21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C22">
         <v>0.9970628023147583</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1532,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1549,19 +1681,25 @@
       <c r="N22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1576,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1593,19 +1731,25 @@
       <c r="N23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C24">
         <v>0.997830331325531</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1620,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1637,19 +1781,25 @@
       <c r="N24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C25">
         <v>0.9920629858970642</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1664,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1681,19 +1831,25 @@
       <c r="N25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C26">
         <v>0.9977728724479675</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1708,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1725,19 +1881,25 @@
       <c r="N26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C27">
         <v>0.9963591694831848</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1752,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1769,19 +1931,25 @@
       <c r="N27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C28">
         <v>0.9988676905632019</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1796,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1813,19 +1981,25 @@
       <c r="N28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C29">
         <v>0.9974004626274109</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1840,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1857,63 +2031,75 @@
       <c r="N29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C30">
         <v>0.9958569407463074</v>
       </c>
       <c r="D30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
+        <v>79</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" t="s">
         <v>76</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" t="s">
-        <v>77</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>1</v>
-      </c>
-      <c r="N30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" t="s">
-        <v>74</v>
       </c>
       <c r="C31">
         <v>0.9776134490966797</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1928,36 +2114,42 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
+        <v>79</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
         <v>77</v>
       </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
-      <c r="N31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" t="s">
-        <v>75</v>
-      </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1972,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1988,6 +2180,12 @@
       </c>
       <c r="N32">
         <v>2</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/template/t9_ocr_report.xlsx
+++ b/template/t9_ocr_report.xlsx
@@ -64,97 +64,97 @@
     <t>is_double</t>
   </si>
   <si>
-    <t>micro_0049_XII.jpg</t>
-  </si>
-  <si>
-    <t>micro_0048_XI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0045_XF.jpg</t>
-  </si>
-  <si>
-    <t>micro_0033_X4.jpg</t>
-  </si>
-  <si>
-    <t>micro_0047_X3.jpg</t>
-  </si>
-  <si>
-    <t>micro_0042_X_O.jpg</t>
-  </si>
-  <si>
-    <t>micro_0016_S_I1362_202.jpg</t>
-  </si>
-  <si>
-    <t>micro_0038_SI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0023_SF.jpg</t>
-  </si>
-  <si>
-    <t>micro_0005_S4.jpg</t>
-  </si>
-  <si>
-    <t>micro_0035_S3.jpg</t>
-  </si>
-  <si>
-    <t>micro_0026_S.jpg</t>
-  </si>
-  <si>
-    <t>micro_0014_FXI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0017_FSII.jpg</t>
-  </si>
-  <si>
-    <t>micro_0019_D9.jpg</t>
-  </si>
-  <si>
-    <t>micro_0025_D8.jpg</t>
-  </si>
-  <si>
-    <t>micro_0037_D7.jpg</t>
+    <t>micro_0047_XⅡI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0046_XI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0043_XF.jpg</t>
+  </si>
+  <si>
+    <t>micro_0031_X4.jpg</t>
+  </si>
+  <si>
+    <t>micro_0045_X3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0040_X.jpg</t>
+  </si>
+  <si>
+    <t>micro_0015_S_1362_202.jpg</t>
+  </si>
+  <si>
+    <t>micro_0036_S_I.jpg</t>
+  </si>
+  <si>
+    <t>micro_0022_SF.jpg</t>
+  </si>
+  <si>
+    <t>micro_0019_S4.jpg</t>
+  </si>
+  <si>
+    <t>micro_0033_S3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0025_S.jpg</t>
+  </si>
+  <si>
+    <t>micro_0013_FXI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0016_FSⅡI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0003_D9.jpg</t>
+  </si>
+  <si>
+    <t>micro_0009_D8.jpg</t>
+  </si>
+  <si>
+    <t>micro_0035_D7.jpg</t>
   </si>
   <si>
     <t>micro_0001_D6.jpg</t>
   </si>
   <si>
-    <t>micro_0040_D5.jpg</t>
-  </si>
-  <si>
-    <t>micro_0031_D4.jpg</t>
-  </si>
-  <si>
-    <t>micro_0044_D3.jpg</t>
-  </si>
-  <si>
-    <t>micro_0002_D2.jpg</t>
-  </si>
-  <si>
-    <t>micro_0027_D18.jpg</t>
-  </si>
-  <si>
-    <t>micro_0012_D16.jpg</t>
-  </si>
-  <si>
-    <t>micro_0050_D15.jpg</t>
-  </si>
-  <si>
-    <t>micro_0008_D14.jpg</t>
-  </si>
-  <si>
-    <t>micro_0021_D13.jpg</t>
-  </si>
-  <si>
-    <t>micro_0053_D12.jpg</t>
-  </si>
-  <si>
-    <t>micro_0022_D11.jpg</t>
-  </si>
-  <si>
-    <t>micro_0024_D10.jpg</t>
-  </si>
-  <si>
-    <t>micro_0036_D1.jpg</t>
+    <t>micro_0038_D5.jpg</t>
+  </si>
+  <si>
+    <t>micro_0029_D4.jpg</t>
+  </si>
+  <si>
+    <t>micro_0037_D3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0028_D2.jpg</t>
+  </si>
+  <si>
+    <t>micro_0026_D18.jpg</t>
+  </si>
+  <si>
+    <t>micro_0052_D16.jpg</t>
+  </si>
+  <si>
+    <t>micro_0048_D15.jpg</t>
+  </si>
+  <si>
+    <t>micro_0007_D14.jpg</t>
+  </si>
+  <si>
+    <t>micro_0050_D13.jpg</t>
+  </si>
+  <si>
+    <t>micro_0051_D12.jpg</t>
+  </si>
+  <si>
+    <t>micro_0021_D11.jpg</t>
+  </si>
+  <si>
+    <t>micro_0023_D10.jpg</t>
+  </si>
+  <si>
+    <t>micro_0034_D1.jpg</t>
   </si>
   <si>
     <t>XⅡ</t>
@@ -646,7 +646,7 @@
         <v>47</v>
       </c>
       <c r="C2">
-        <v>0.8170149326324463</v>
+        <v>0.8689644336700439</v>
       </c>
       <c r="D2" t="s">
         <v>78</v>
@@ -696,7 +696,7 @@
         <v>48</v>
       </c>
       <c r="C3">
-        <v>0.8569067716598511</v>
+        <v>0.9491414427757263</v>
       </c>
       <c r="D3" t="s">
         <v>78</v>
@@ -746,7 +746,7 @@
         <v>49</v>
       </c>
       <c r="C4">
-        <v>0.9116420149803162</v>
+        <v>0.8894996047019958</v>
       </c>
       <c r="D4" t="s">
         <v>78</v>
@@ -796,7 +796,7 @@
         <v>50</v>
       </c>
       <c r="C5">
-        <v>0.9954218864440918</v>
+        <v>0.9899726510047913</v>
       </c>
       <c r="D5" t="s">
         <v>78</v>
@@ -846,7 +846,7 @@
         <v>51</v>
       </c>
       <c r="C6">
-        <v>0.9854831695556641</v>
+        <v>0.9783388376235962</v>
       </c>
       <c r="D6" t="s">
         <v>78</v>
@@ -946,7 +946,7 @@
         <v>53</v>
       </c>
       <c r="C8">
-        <v>0.8611977100372314</v>
+        <v>0.8279581665992737</v>
       </c>
       <c r="D8" t="s">
         <v>78</v>
@@ -996,7 +996,7 @@
         <v>54</v>
       </c>
       <c r="C9">
-        <v>0.9470760822296143</v>
+        <v>0.9187681674957275</v>
       </c>
       <c r="D9" t="s">
         <v>78</v>
@@ -1046,7 +1046,7 @@
         <v>55</v>
       </c>
       <c r="C10">
-        <v>0.9956051707267761</v>
+        <v>0.9974538087844849</v>
       </c>
       <c r="D10" t="s">
         <v>78</v>
@@ -1096,7 +1096,7 @@
         <v>56</v>
       </c>
       <c r="C11">
-        <v>0.9962334036827087</v>
+        <v>0.9970991611480713</v>
       </c>
       <c r="D11" t="s">
         <v>78</v>
@@ -1146,7 +1146,7 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>0.9953106641769409</v>
+        <v>0.9960719347000122</v>
       </c>
       <c r="D12" t="s">
         <v>78</v>
@@ -1196,7 +1196,7 @@
         <v>58</v>
       </c>
       <c r="C13">
-        <v>0.9655420184135437</v>
+        <v>0.9499724507331848</v>
       </c>
       <c r="D13" t="s">
         <v>78</v>
@@ -1246,7 +1246,7 @@
         <v>59</v>
       </c>
       <c r="C14">
-        <v>0.9048388004302979</v>
+        <v>0.8811050653457642</v>
       </c>
       <c r="D14" t="s">
         <v>78</v>
@@ -1296,7 +1296,7 @@
         <v>60</v>
       </c>
       <c r="C15">
-        <v>0.8947662115097046</v>
+        <v>0.8644741773605347</v>
       </c>
       <c r="D15" t="s">
         <v>78</v>
@@ -1346,7 +1346,7 @@
         <v>61</v>
       </c>
       <c r="C16">
-        <v>0.994773268699646</v>
+        <v>0.9962631464004517</v>
       </c>
       <c r="D16" t="s">
         <v>78</v>
@@ -1396,7 +1396,7 @@
         <v>62</v>
       </c>
       <c r="C17">
-        <v>0.994149923324585</v>
+        <v>0.9893554449081421</v>
       </c>
       <c r="D17" t="s">
         <v>78</v>
@@ -1446,7 +1446,7 @@
         <v>63</v>
       </c>
       <c r="C18">
-        <v>0.9946953058242798</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
         <v>78</v>
@@ -1496,7 +1496,7 @@
         <v>64</v>
       </c>
       <c r="C19">
-        <v>0.9986534118652344</v>
+        <v>0.9894293546676636</v>
       </c>
       <c r="D19" t="s">
         <v>78</v>
@@ -1546,7 +1546,7 @@
         <v>65</v>
       </c>
       <c r="C20">
-        <v>0.9924682974815369</v>
+        <v>0.9951184988021851</v>
       </c>
       <c r="D20" t="s">
         <v>78</v>
@@ -1596,7 +1596,7 @@
         <v>66</v>
       </c>
       <c r="C21">
-        <v>0.9967378377914429</v>
+        <v>0.9986019134521484</v>
       </c>
       <c r="D21" t="s">
         <v>78</v>
@@ -1646,7 +1646,7 @@
         <v>67</v>
       </c>
       <c r="C22">
-        <v>0.9970628023147583</v>
+        <v>0.9940056800842285</v>
       </c>
       <c r="D22" t="s">
         <v>78</v>
@@ -1670,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>1</v>
@@ -1696,7 +1696,7 @@
         <v>68</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0.9909565448760986</v>
       </c>
       <c r="D23" t="s">
         <v>78</v>
@@ -1746,7 +1746,7 @@
         <v>69</v>
       </c>
       <c r="C24">
-        <v>0.997830331325531</v>
+        <v>0.9964165091514587</v>
       </c>
       <c r="D24" t="s">
         <v>78</v>
@@ -1796,7 +1796,7 @@
         <v>70</v>
       </c>
       <c r="C25">
-        <v>0.9920629858970642</v>
+        <v>0.9880501627922058</v>
       </c>
       <c r="D25" t="s">
         <v>78</v>
@@ -1846,7 +1846,7 @@
         <v>71</v>
       </c>
       <c r="C26">
-        <v>0.9977728724479675</v>
+        <v>0.9982282519340515</v>
       </c>
       <c r="D26" t="s">
         <v>78</v>
@@ -1896,7 +1896,7 @@
         <v>72</v>
       </c>
       <c r="C27">
-        <v>0.9963591694831848</v>
+        <v>0.9942888617515564</v>
       </c>
       <c r="D27" t="s">
         <v>78</v>
@@ -1946,7 +1946,7 @@
         <v>73</v>
       </c>
       <c r="C28">
-        <v>0.9988676905632019</v>
+        <v>0.9988810420036316</v>
       </c>
       <c r="D28" t="s">
         <v>78</v>
@@ -1996,7 +1996,7 @@
         <v>74</v>
       </c>
       <c r="C29">
-        <v>0.9974004626274109</v>
+        <v>0.9973005652427673</v>
       </c>
       <c r="D29" t="s">
         <v>78</v>
@@ -2046,7 +2046,7 @@
         <v>75</v>
       </c>
       <c r="C30">
-        <v>0.9958569407463074</v>
+        <v>0.9884665608406067</v>
       </c>
       <c r="D30" t="s">
         <v>78</v>
@@ -2096,7 +2096,7 @@
         <v>76</v>
       </c>
       <c r="C31">
-        <v>0.9776134490966797</v>
+        <v>0.9512179493904114</v>
       </c>
       <c r="D31" t="s">
         <v>78</v>
@@ -2117,13 +2117,13 @@
         <v>79</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31">
         <v>1</v>

--- a/template/t9_ocr_report.xlsx
+++ b/template/t9_ocr_report.xlsx
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -776,10 +776,10 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -926,10 +926,10 @@
         <v>1</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -976,10 +976,10 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1076,10 +1076,10 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1126,10 +1126,10 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1367,19 +1367,19 @@
         <v>79</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -1479,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -1579,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -1667,19 +1667,19 @@
         <v>79</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -1879,7 +1879,7 @@
         <v>2</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -1929,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -2117,19 +2117,19 @@
         <v>79</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -2167,19 +2167,19 @@
         <v>79</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32">
         <v>1</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
